--- a/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé va à la fête. Papa vient avec lui. Papa est l'accompagnant. Noé aime rester avec l'accompagnant. Il marche à côté de papa. Papa tient la main. Ils voient des ballons. Noé reste près. Papa dit : tu restes avec moi. Noé hoche la tête. Il sent la main de papa. Ils écoutent une chanson. Noé reste avec papa. L'adulte connu est là. Noé est calme. Il sourit.</t>
+          <t>Noé va à la fête. Papa vient avec lui. Papa est l'accompagnant. Noé aime rester avec l'accompagnant. Il marche à côté de papa. Papa tient la main. Ils voient des ballons. Noé reste près. Tu restes avec moi. Noé hoche la tête. Il sent la main de papa. Ils écoutent une chanson. Noé reste avec papa. L'adulte connu est là. Noé est calme. Il sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va à la fête. Papa vient avec lui. Papa est l'accompagnant. Noé aime rester avec l'accompagnant. Il marche à côté de papa. Papa tient la main. Ils voient des ballons. Noé reste près.
+papa|Tu restes avec moi.
+narrateur|Noé hoche la tête. Il sent la main de papa. Ils écoutent une chanson. Noé reste avec papa. L'adulte connu est là. Noé est calme. Il sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est à la fête. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé reste avec papa. L'accompagnant est là. La main est tenue.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé et papa regardent les ballons. Ils rentrent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Noé hoche la tête. Il sent la main de papa. Ils écoutent une chanson. Noé reste avec papa. L'adulte connu est là. Noé est calme. Il sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Noé est à la fête. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Noé reste avec papa. L'accompagnant est là. La main est tenue.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Noé et papa regardent les ballons. Ils rentrent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noé reste avec papa</t>
+          <t>Le fanion et la main de papa</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le fanion tremble. Victorino va à la fête. Il reste avec papa, la main tenue.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé va à la fête. Papa vient avec lui. Papa est l'accompagnant. Noé aime rester avec l'accompagnant. Il marche à côté de papa. Papa tient la main. Ils voient des ballons. Noé reste près. Tu restes avec moi. Noé hoche la tête. Il sent la main de papa. Ils écoutent une chanson. Noé reste avec papa. L'adulte connu est là. Noé est calme. Il sourit.</t>
+          <t>Un fanion en papier tremble à la fenêtre. Il est rouge et jaune. La ficelle fait un tout petit bruit. Ça sent le gâteau, dans la cuisine. Une miette sucrée brille sur la table. Victorino vit avec papa et maman. Le manteau est prêt, Victorino. On va à la fête ? Oui. On y va ensemble. Tu restes avec papa. Oui, maman. En ce moment, Victorino met le manteau. Le bouton est un peu froid. Papa vient avec lui. Ils marchent vers la cour. Papa est l'accompagnant. Victorino aime rester avec l'accompagnant. Il marche à côté de papa. Papa tient la main. La main est chaude. Les pieds restent près de papa. Ils arrivent dans la cour. Ils voient des ballons. Un ballon bleu tape doucement. La ficelle du ballon chatouille le nez. Ça sent le gâteau, aussi, ici. Il est bleu, papa. Oui. Tu restes avec moi. Victorino reste près. Il hoche la tête. Il sent la main de papa. Ils écoutent une chanson. La chanson est douce. Ça chante. Oui. On écoute ensemble. Un tambour fait un petit toum. Tu entends le tambour ? Oui. On l'écoute, tout près. Victorino reste avec papa. L'adulte connu est là. Bravo. Tu restes à côté. Victorino est calme. Les ballons dansent un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé va à la fête. Papa vient avec lui. Papa est l'accompagnant. Noé aime rester avec l'accompagnant. Il marche à côté de papa. Papa tient la main. Ils voient des ballons. Noé reste près.
+          <t>narrateur|Un fanion en papier tremble à la fenêtre.
+narrateur|Il est rouge et jaune.
+narrateur|La ficelle fait un tout petit bruit.
+narrateur|Ça sent le gâteau, dans la cuisine.
+narrateur|Une miette sucrée brille sur la table.
+narrateur|Victorino vit avec papa et maman.
+maman|Le manteau est prêt, Victorino.
+enfant-m|On va à la fête ?
+papa|Oui.
+papa|On y va ensemble.
+maman|Tu restes avec papa.
+enfant-m|Oui, maman.
+narrateur|En ce moment, Victorino met le manteau.
+narrateur|Le bouton est un peu froid.
+narrateur|Papa vient avec lui.
+narrateur|Ils marchent vers la cour.
+narrateur|Papa est l'accompagnant.
+narrateur|Victorino aime rester avec l'accompagnant.
+narrateur|Il marche à côté de papa.
+narrateur|Papa tient la main.
+narrateur|La main est chaude.
+narrateur|Les pieds restent près de papa.
+narrateur|Ils arrivent dans la cour.
+narrateur|Ils voient des ballons.
+narrateur|Un ballon bleu tape doucement.
+narrateur|La ficelle du ballon chatouille le nez.
+narrateur|Ça sent le gâteau, aussi, ici.
+enfant-m|Il est bleu, papa.
+papa|Oui.
 papa|Tu restes avec moi.
-narrateur|Noé hoche la tête. Il sent la main de papa. Ils écoutent une chanson. Noé reste avec papa. L'adulte connu est là. Noé est calme. Il sourit.</t>
+narrateur|Victorino reste près.
+narrateur|Il hoche la tête.
+narrateur|Il sent la main de papa.
+narrateur|Ils écoutent une chanson.
+narrateur|La chanson est douce.
+enfant-m|Ça chante.
+papa|Oui.
+papa|On écoute ensemble.
+narrateur|Un tambour fait un petit toum.
+papa|Tu entends le tambour ?
+enfant-m|Oui.
+papa|On l'écoute, tout près.
+narrateur|Victorino reste avec papa.
+narrateur|L'adulte connu est là.
+papa|Bravo.
+papa|Tu restes à côté.
+narrateur|Victorino est calme.
+narrateur|Les ballons dansent un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé est à la fête. Que fait-il ?</t>
+          <t>Victorino est à la fête. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1559,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé est à la fête. Que fait-il ?</t>
+          <t>narrateur|Victorino est à la fête.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé reste avec papa. L'accompagnant est là. La main est tenue.</t>
+          <t>Victorino reste avec papa. L'accompagnant est là. La main est tenue. Tu restes avec moi ? Oui, papa. Bravo, Victorino. Tu restes avec l'adulte connu. Le ballon bleu tape encore. Le tambour fait un dernier toum. Je reste près. Oui. C'est bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1736,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé reste avec papa. L'accompagnant est là. La main est tenue.</t>
+          <t>narrateur|Victorino reste avec papa.
+narrateur|L'accompagnant est là.
+narrateur|La main est tenue.
+papa|Tu restes avec moi ?
+enfant-m|Oui, papa.
+papa|Bravo, Victorino.
+papa|Tu restes avec l'adulte connu.
+narrateur|Le ballon bleu tape encore.
+narrateur|Le tambour fait un dernier toum.
+enfant-m|Je reste près.
+papa|Oui.
+papa|C'est bien.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé et papa regardent les ballons. Ils rentrent ensemble.</t>
+          <t>Victorino et papa regardent les ballons. On rentre ensemble ? Oui. Ils rentrent ensemble. Les chaussures font un petit bruit sur le chemin. Maman ouvre la porte. Ça sent encore le gâteau. Vous voilà. Tu es resté avec papa ? Oui, maman. Bravo. Tu as fait du bon travail. La main était tenue. Le ballon était bleu. Oui. Le fanion tremble encore à la fenêtre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1915,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé et papa regardent les ballons. Ils rentrent ensemble.</t>
+          <t>narrateur|Victorino et papa regardent les ballons.
+papa|On rentre ensemble ?
+enfant-m|Oui.
+narrateur|Ils rentrent ensemble.
+narrateur|Les chaussures font un petit bruit sur le chemin.
+narrateur|Maman ouvre la porte.
+narrateur|Ça sent encore le gâteau.
+maman|Vous voilà.
+maman|Tu es resté avec papa ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|La main était tenue.
+enfant-m|Le ballon était bleu.
+maman|Oui.
+narrateur|Le fanion tremble encore à la fenêtre.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis resté avec papa. Bravo. Tu as fait du bon travail. Le fanion tremble encore à la fenêtre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2098,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je suis resté avec papa.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le fanion tremble encore à la fenêtre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé va à la fête. Papa vient avec lui. Papa est l'accompagnant. Noé aime &lt;emphasis level="moderate"&gt;rester&lt;/emphasis&gt; avec l'accompagnant. Il marche à côté de papa. Papa tient la main. Ils voient des ballons. Noé reste près. Papa dit : tu restes avec moi. Noé hoche la tête. Il sent la main de papa. Ils écoutent une chanson. Noé reste avec papa. L'adulte connu est là. Noé est calme. Il sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un fanion en papier tremble à la fenêtre. Il est rouge et jaune. La ficelle fait un tout petit bruit. Ça sent le gâteau, dans la cuisine. Une miette sucrée brille sur la table. Victorino vit avec papa et maman. Le manteau est prêt, Victorino. On va à la fête ? Oui. On y va ensemble. Tu restes avec papa. Oui, maman. En ce moment, Victorino met le manteau. Le bouton est un peu froid. Papa vient avec lui. Ils marchent vers la cour. Papa est l'accompagnant. Victorino aime rester avec l'accompagnant. Il marche à côté de papa. Papa tient la main. La main est chaude. Les pieds restent près de papa. Ils arrivent dans la cour. Ils voient des ballons. Un ballon bleu tape doucement. La ficelle du ballon chatouille le nez. Ça sent le gâteau, aussi, ici. Il est bleu, papa. Oui. Tu restes avec moi. Victorino reste près. Il hoche la tête. Il sent la main de papa. Ils écoutent une chanson. La chanson est douce. Ça chante. Oui. On écoute ensemble. Un tambour fait un petit toum. Tu entends le tambour ? Oui. On l'écoute, tout près. Victorino reste avec papa. L'adulte connu est là. Bravo. Tu restes à côté. Victorino est calme. Les ballons dansent un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1374,7 +1374,6 @@
 narrateur|Les ballons dansent un peu.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1404,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Noé est à la fête. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino est à la fête. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1563,7 +1562,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1593,7 +1591,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Noé reste avec papa. L'accompagnant est là. La &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est tenue.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino reste avec papa. L'accompagnant est là. La main est tenue. Tu restes avec moi ? Oui, papa. Bravo, Victorino. Tu restes avec l'adulte connu. Le ballon bleu tape encore. Le tambour fait un dernier toum. Je reste près. Oui. C'est bien.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,7 +1748,6 @@
 papa|C'est bien.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1775,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino et papa regardent les ballons. On rentre ensemble ? Oui. Ils rentrent ensemble. Les chaussures font un petit bruit sur le chemin. Maman ouvre la porte. Ça sent encore le gâteau. Vous voilà. Tu es resté avec papa ? Oui, maman. Bravo. Tu as fait du bon travail. La main était tenue. Le ballon était bleu. Oui. Le fanion tremble encore à la fenêtre.</t>
+          <t>Victorino et papa regardent les ballons. On rentre ensemble ? Oui. Ils rentrent ensemble. Les chaussures font un petit bruit sur le chemin. Maman ouvre la porte. Ça sent encore le gâteau. Vous voilà. Tu es resté avec papa ? Oui, maman. Bravo. La main était tenue. Le ballon était bleu. Oui. Le fanion tremble encore à la fenêtre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Noé et papa regardent les ballons. Ils rentrent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino et papa regardent les ballons. On rentre ensemble ? Oui. Ils rentrent ensemble. Les chaussures font un petit bruit sur le chemin. Maman ouvre la porte. Ça sent encore le gâteau. Vous voilà. Tu es resté avec papa ? Oui, maman. Bravo. La main était tenue. Le ballon était bleu. Oui. Le fanion tremble encore à la fenêtre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,14 +1923,12 @@
 maman|Tu es resté avec papa ?
 enfant-m|Oui, maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 papa|La main était tenue.
 enfant-m|Le ballon était bleu.
 maman|Oui.
 narrateur|Le fanion tremble encore à la fenêtre.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis resté avec papa. Bravo. Tu as fait du bon travail. Le fanion tremble encore à la fenêtre. L'histoire est finie.</t>
+          <t>Je suis resté avec papa. Bravo. Le fanion tremble encore à la fenêtre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis resté avec papa. Bravo. Le fanion tremble encore à la fenêtre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,12 +2095,9 @@
         <is>
           <t>enfant-m|Je suis resté avec papa.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le fanion tremble encore à la fenêtre.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le fanion tremble encore à la fenêtre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fête de l'école</t>
+          <t>maison puis fête de l'école</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, papa</t>
+          <t>Victorino, papa, maman</t>
         </is>
       </c>
     </row>
